--- a/src/nodes/HPC/compressor_stage_7_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_7_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-13.998687832755474</v>
+        <v>-14.0031823621086</v>
       </c>
       <c r="B1">
-        <v>5.7104718698165664</v>
+        <v>5.6994415295213869</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-12.877104625293999</v>
+        <v>-12.903177521867193</v>
       </c>
       <c r="B2">
-        <v>6.1213883979416375</v>
+        <v>6.0665790898396263</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-11.956538228601996</v>
+        <v>-11.990645197724827</v>
       </c>
       <c r="B3">
-        <v>6.1107567671932337</v>
+        <v>6.0397734034498436</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-11.066090991475642</v>
+        <v>-11.106344054126073</v>
       </c>
       <c r="B4">
-        <v>6.0369628754721552</v>
+        <v>5.9536444458245361</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-10.196262817464183</v>
+        <v>-10.241421577267026</v>
       </c>
       <c r="B5">
-        <v>5.9199291767891271</v>
+        <v>5.8267943465024858</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-9.34318007225826</v>
+        <v>-9.3922679639001121</v>
       </c>
       <c r="B6">
-        <v>5.7677789888159658</v>
+        <v>5.6668085246209481</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-8.5046315616881376</v>
+        <v>-8.556822487828164</v>
       </c>
       <c r="B7">
-        <v>5.5851493607009441</v>
+        <v>5.4780172638160582</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-7.6793170180013695</v>
+        <v>-7.7338732310405822</v>
       </c>
       <c r="B8">
-        <v>5.3747670568126118</v>
+        <v>5.262967214262332</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-6.8652040684385556</v>
+        <v>-6.9215261398670691</v>
       </c>
       <c r="B9">
-        <v>5.1408941236514023</v>
+        <v>5.0256384241707854</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.0600985172318005</v>
+        <v>-6.1177363915785179</v>
       </c>
       <c r="B10">
-        <v>4.8881319633718165</v>
+        <v>4.77032775860521</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.2618909815861548</v>
+        <v>-5.32053822287026</v>
       </c>
       <c r="B11">
-        <v>4.6209041186127342</v>
+        <v>4.5011659520039924</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.4694552941968242</v>
+        <v>-4.528882037348426</v>
       </c>
       <c r="B12">
-        <v>4.3415722513272117</v>
+        <v>4.2203585618522323</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.685513336746685</v>
+        <v>-3.7453038468379236</v>
       </c>
       <c r="B13">
-        <v>4.0444283602406434</v>
+        <v>3.9225765684472984</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.9116929343669113</v>
+        <v>-2.9713202469402269</v>
       </c>
       <c r="B14">
-        <v>3.7260587672413119</v>
+        <v>3.6046330908126181</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.1413976369941441</v>
+        <v>-2.2007845601442764</v>
       </c>
       <c r="B15">
-        <v>3.400296750096695</v>
+        <v>3.279444380063592</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.3685772147190647</v>
+        <v>-1.4280590858021196</v>
       </c>
       <c r="B16">
-        <v>3.0798301196882516</v>
+        <v>2.9588571545536033</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-0.59759059344299015</v>
+        <v>-0.65720530383069664</v>
       </c>
       <c r="B17">
-        <v>2.7555178634741235</v>
+        <v>2.6343368694959581</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>0.16593326740996064</v>
+        <v>0.10653188187393758</v>
       </c>
       <c r="B18">
-        <v>2.4155556081159424</v>
+        <v>2.2948622055395496</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.92169443013510322</v>
+        <v>0.86287305206419618</v>
       </c>
       <c r="B19">
-        <v>2.0593143605125834</v>
+        <v>1.9398460082156839</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.6707252124576262</v>
+        <v>1.6127801586546213</v>
       </c>
       <c r="B20">
-        <v>1.6889589726222327</v>
+        <v>1.5713096642762638</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.4140579321027031</v>
+        <v>2.3572151535597423</v>
       </c>
       <c r="B21">
-        <v>1.3066542964030756</v>
+        <v>1.1912745604731991</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.152541105696864</v>
+        <v>3.0969687089409743</v>
       </c>
       <c r="B22">
-        <v>0.91417973836502076</v>
+        <v>0.80140216679061349</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>3.8862880454719924</v>
+        <v>3.8321463779472191</v>
       </c>
       <c r="B23">
-        <v>0.51177292322486934</v>
+        <v>0.40191428614152319</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4.6152282625613248</v>
+        <v>4.5626824339742633</v>
       </c>
       <c r="B24">
-        <v>0.099286030251139135</v>
+        <v>-0.00732719532884089</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5.3392912680980915</v>
+        <v>5.288511150417885</v>
       </c>
       <c r="B25">
-        <v>-0.32342876128764747</v>
+        <v>-0.42646039147524351</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>6.0583761935988374</v>
+        <v>6.0095384782087917</v>
       </c>
       <c r="B26">
-        <v>-0.756582980583118</v>
+        <v>-0.85568293124338624</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>6.772260652113399</v>
+        <v>6.7255570784174266</v>
       </c>
       <c r="B27">
-        <v>-1.2006429906675122</v>
+        <v>-1.2954305039427267</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>7.4806918770749311</v>
+        <v>7.436331289649158</v>
       </c>
       <c r="B28">
-        <v>-1.6561388630332199</v>
+        <v>-1.7461983139736594</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>8.18341710191658</v>
+        <v>8.1416254505093537</v>
       </c>
       <c r="B29">
-        <v>-2.1236006691726295</v>
+        <v>-2.2084815657365757</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>8.8803202912843062</v>
+        <v>8.8413312892267744</v>
       </c>
       <c r="B30">
-        <v>-2.6032717444051703</v>
+        <v>-2.6825077748907</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>9.5718323346753031</v>
+        <v>9.53585009252377</v>
       </c>
       <c r="B31">
-        <v>-3.094248479358447</v>
+        <v>-3.1674337021306003</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>10.258520852799581</v>
+        <v>10.225710536746096</v>
       </c>
       <c r="B32">
-        <v>-3.59534052848711</v>
+        <v>-3.6621484194096769</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>10.940953466367136</v>
+        <v>10.91144129823949</v>
       </c>
       <c r="B33">
-        <v>-4.1053575462458012</v>
+        <v>-4.1655409986813261</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>11.619476548610157</v>
+        <v>11.5933648807315</v>
       </c>
       <c r="B34">
-        <v>-4.623573160557731</v>
+        <v>-4.6769337503932507</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>12.293551482849527</v>
+        <v>12.270979097476854</v>
       </c>
       <c r="B35">
-        <v>-5.1511168932203466</v>
+        <v>-5.19738193897035</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>12.962418404928307</v>
+        <v>12.943575589112072</v>
       </c>
       <c r="B36">
-        <v>-5.6895822394996562</v>
+        <v>-5.7283740673318251</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>13.625317450689575</v>
+        <v>13.610445996273684</v>
       </c>
       <c r="B37">
-        <v>-6.2405626946616763</v>
+        <v>-6.2713986383968843</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>14.280946352170325</v>
+        <v>14.270376537702189</v>
       </c>
       <c r="B38">
-        <v>-6.8067892176747717</v>
+        <v>-6.8290062176569926</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>14.925833226183267</v>
+        <v>14.920131744553979</v>
       </c>
       <c r="B39">
-        <v>-7.3955426223167624</v>
+        <v>-7.4079956208926934</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>15.555963785735051</v>
+        <v>15.555970726089425</v>
       </c>
       <c r="B40">
-        <v>-8.01524118606782</v>
+        <v>-8.0162277264567923</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>16.167323743832323</v>
+        <v>16.174152591568895</v>
       </c>
       <c r="B41">
-        <v>-8.67430318640812</v>
+        <v>-8.6615634127021</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>16.167323743832323</v>
+        <v>16.174152591568895</v>
       </c>
       <c r="B42">
-        <v>-8.67430318640812</v>
+        <v>-8.6615634127021</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>15.36656473897486</v>
+        <v>15.379490389978415</v>
       </c>
       <c r="B43">
-        <v>-8.412425974486899</v>
+        <v>-8.3870726803430777</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>14.579562921029826</v>
+        <v>14.597480174316056</v>
       </c>
       <c r="B44">
-        <v>-8.1216988529883825</v>
+        <v>-8.0859958407639549</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>13.802316445319443</v>
+        <v>13.824393475597466</v>
       </c>
       <c r="B45">
-        <v>-7.8105140068724292</v>
+        <v>-7.7661676700029032</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>13.030823467165922</v>
+        <v>13.056501824838286</v>
       </c>
       <c r="B46">
-        <v>-7.4872636210988954</v>
+        <v>-7.4354229440980957</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>12.261624098390804</v>
+        <v>12.290581728382589</v>
       </c>
       <c r="B47">
-        <v>-7.1592033549629228</v>
+        <v>-7.1005353149051924</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>11.493426276812917</v>
+        <v>11.525429593888159</v>
       </c>
       <c r="B48">
-        <v>-6.8290427651008025</v>
+        <v>-6.7640339375498195</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>10.72547989675039</v>
+        <v>10.760346804341205</v>
       </c>
       <c r="B49">
-        <v>-6.4983548824841044</v>
+        <v>-6.4273868429750829</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>9.9570348525213674</v>
+        <v>9.9946347427279427</v>
       </c>
       <c r="B50">
-        <v>-6.1687127380844062</v>
+        <v>-6.0920620621240964</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>9.1875617991425713</v>
+        <v>9.22780047867792</v>
       </c>
       <c r="B51">
-        <v>-5.8412264102193321</v>
+        <v>-5.7590954086434643</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>8.4174144344249964</v>
+        <v>8.4601738283940016</v>
       </c>
       <c r="B52">
-        <v>-5.5151541665906958</v>
+        <v>-5.4277938269937431</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>7.6471672168782261</v>
+        <v>7.692290294722393</v>
       </c>
       <c r="B53">
-        <v>-5.1892913222463593</v>
+        <v>-5.0970320443389854</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>6.87739460501183</v>
+        <v>6.9246853805092892</v>
       </c>
       <c r="B54">
-        <v>-4.862433192234187</v>
+        <v>-4.7656847878432433</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>6.1085338664660469</v>
+        <v>6.1577667400805245</v>
       </c>
       <c r="B55">
-        <v>-4.5336627917111034</v>
+        <v>-4.432895437709667</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5.3404735054037831</v>
+        <v>5.3914306336804891</v>
       </c>
       <c r="B56">
-        <v>-4.2032139362702967</v>
+        <v>-4.098881986297835</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4.5729648351186087</v>
+        <v>4.6254454730332064</v>
       </c>
       <c r="B57">
-        <v>-3.8716081416140184</v>
+        <v>-3.7641310790064253</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3.80575916890409</v>
+        <v>3.8595796698626947</v>
       </c>
       <c r="B58">
-        <v>-3.5393669234445184</v>
+        <v>-3.4291293612341165</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.03863774861822</v>
+        <v>3.0936295080511313</v>
       </c>
       <c r="B59">
-        <v>-3.2069490348961569</v>
+        <v>-3.0943049095359689</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.2715015303767134</v>
+        <v>2.3275027601133345</v>
       </c>
       <c r="B60">
-        <v>-2.8745621788317441</v>
+        <v>-2.759851525092583</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.5042813988597132</v>
+        <v>1.5611350707222804</v>
       </c>
       <c r="B61">
-        <v>-2.5423512955462026</v>
+        <v>-2.4259044402409415</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.73690823874735489</v>
+        <v>0.79446208455093659</v>
       </c>
       <c r="B62">
-        <v>-2.2104613253344474</v>
+        <v>-2.0925988873180223</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.030503731001108578</v>
+        <v>0.027590259977252153</v>
       </c>
       <c r="B63">
-        <v>-1.8786527420006629</v>
+        <v>-1.7597111612180403</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.797106954310006</v>
+        <v>-0.73869068980095276</v>
       </c>
       <c r="B64">
-        <v>-1.5451481533860711</v>
+        <v>-1.425581807064122</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.561870540824547</v>
+        <v>-1.5034202378808759</v>
       </c>
       <c r="B65">
-        <v>-1.20778570084116</v>
+        <v>-1.08819243253663</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.3237636001899524</v>
+        <v>-2.2656378573597267</v>
       </c>
       <c r="B66">
-        <v>-0.86440352571641144</v>
+        <v>-0.74552464531592055</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.0830878737015008</v>
+        <v>-3.0256247680953452</v>
       </c>
       <c r="B67">
-        <v>-0.5156344033851693</v>
+        <v>-0.39816938356265569</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-3.8454756292547452</v>
+        <v>-3.7886291769881351</v>
       </c>
       <c r="B68">
-        <v>-0.17328964531220112</v>
+        <v>-0.057154907358695356</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-4.6152896455111012</v>
+        <v>-4.5587164103486479</v>
       </c>
       <c r="B69">
-        <v>0.15348165641785519</v>
+        <v>0.26897615593367807</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-5.3864842175951422</v>
+        <v>-5.33025328508543</v>
       </c>
       <c r="B70">
-        <v>0.47735782333229065</v>
+        <v>0.59206103175167324</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-6.152467835577152</v>
+        <v>-6.0970980556577432</v>
       </c>
       <c r="B71">
-        <v>0.812161773347443</v>
+        <v>0.92500560747078631</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-6.9148742528470448</v>
+        <v>-6.8607732361296589</v>
       </c>
       <c r="B72">
-        <v>1.154467396323879</v>
+        <v>1.2646105654201374</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-7.6764317564307136</v>
+        <v>-7.6238212330845894</v>
       </c>
       <c r="B73">
-        <v>1.498553258475839</v>
+        <v>1.6055334483437933</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-8.4360215045782923</v>
+        <v>-8.3851997635784858</v>
       </c>
       <c r="B74">
-        <v>1.8467656594880149</v>
+        <v>1.9499644456919745</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-9.1915419064099328</v>
+        <v>-9.14295084334604</v>
       </c>
       <c r="B75">
-        <v>2.2035118017367341</v>
+        <v>2.3020179455068939</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-9.94080750330161</v>
+        <v>-9.8950383723643167</v>
       </c>
       <c r="B76">
-        <v>2.5733747648944187</v>
+        <v>2.6659724834925753</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-10.681795145592753</v>
+        <v>-10.639577504821153</v>
       </c>
       <c r="B77">
-        <v>2.960597253893432</v>
+        <v>3.0457887590317463</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-11.41321478722079</v>
+        <v>-11.375366527504992</v>
       </c>
       <c r="B78">
-        <v>3.3678845974098004</v>
+        <v>3.4439919785601116</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-12.132865909645265</v>
+        <v>-12.100355372207012</v>
       </c>
       <c r="B79">
-        <v>3.7998514569524051</v>
+        <v>3.8648900296707955</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-12.836886462042948</v>
+        <v>-12.810945800024632</v>
       </c>
       <c r="B80">
-        <v>4.2645968587060619</v>
+        <v>4.3160440308957861</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-13.515788637790376</v>
+        <v>-13.498297566672934</v>
       </c>
       <c r="B81">
-        <v>4.7820174839411393</v>
+        <v>4.8160303293592319</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-13.998687832755474</v>
+        <v>-14.0031823621086</v>
       </c>
       <c r="B82">
-        <v>5.7104718698165664</v>
+        <v>5.6994415295213869</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-16.705832242249819</v>
+        <v>-16.698091553425037</v>
       </c>
       <c r="B1">
-        <v>5.1442228476678373</v>
+        <v>5.1692937705354778</v>
       </c>
       <c r="C1">
         <v>216.89590882303355</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-15.651772585576849</v>
+        <v>-15.676095562972559</v>
       </c>
       <c r="B2">
-        <v>5.2362123886135317</v>
+        <v>5.1663362393531864</v>
       </c>
       <c r="C2">
         <v>216.89590882303355</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-14.671114732754042</v>
+        <v>-14.707805759805494</v>
       </c>
       <c r="B3">
-        <v>5.1143341806121221</v>
+        <v>5.0076589261335158</v>
       </c>
       <c r="C3">
         <v>216.89590882303355</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-13.701696016095788</v>
+        <v>-13.748019322396393</v>
       </c>
       <c r="B4">
-        <v>4.9597089742327372</v>
+        <v>4.8243263109953274</v>
       </c>
       <c r="C4">
         <v>216.89590882303355</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-12.740062111624246</v>
+        <v>-12.794224136759311</v>
       </c>
       <c r="B5">
-        <v>4.7824014879771362</v>
+        <v>4.6236222072591433</v>
       </c>
       <c r="C5">
         <v>216.89590882303355</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-11.784805244100696</v>
+        <v>-11.845396282568075</v>
       </c>
       <c r="B6">
-        <v>4.5865134973540487</v>
+        <v>4.4085154469734782</v>
       </c>
       <c r="C6">
         <v>216.89590882303355</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-10.835122250304872</v>
+        <v>-10.900951510303351</v>
       </c>
       <c r="B7">
-        <v>4.3743851452611322</v>
+        <v>4.1807000473904115</v>
       </c>
       <c r="C7">
         <v>216.89590882303355</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-9.89054126648623</v>
+        <v>-9.9605464889666777</v>
       </c>
       <c r="B8">
-        <v>4.1473912812639906</v>
+        <v>3.9411714883782714</v>
       </c>
       <c r="C8">
         <v>216.89590882303355</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-8.9503240148725052</v>
+        <v>-9.0236441801353369</v>
       </c>
       <c r="B9">
-        <v>3.9076829942592428</v>
+        <v>3.6914868997643535</v>
       </c>
       <c r="C9">
         <v>216.89590882303355</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-8.0136733009520675</v>
+        <v>-8.0896647128110413</v>
       </c>
       <c r="B10">
-        <v>3.657583036369183</v>
+        <v>3.4333276033856013</v>
       </c>
       <c r="C10">
         <v>216.89590882303355</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-7.0798226772776358</v>
+        <v>-7.15805059311755</v>
       </c>
       <c r="B11">
-        <v>3.3993245732878328</v>
+        <v>3.1683100391586034</v>
       </c>
       <c r="C11">
         <v>216.89590882303355</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-6.1483632904513339</v>
+        <v>-6.2285043666751063</v>
       </c>
       <c r="B12">
-        <v>3.1340988639661456</v>
+        <v>2.8972966688130608</v>
       </c>
       <c r="C12">
         <v>216.89590882303355</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-5.2202859162085984</v>
+        <v>-5.3017463599678569</v>
       </c>
       <c r="B13">
-        <v>2.8590191268110963</v>
+        <v>2.6181989232514917</v>
       </c>
       <c r="C13">
         <v>216.89590882303355</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-4.2961833149209436</v>
+        <v>-4.3782074860507194</v>
       </c>
       <c r="B14">
-        <v>2.5723582608569044</v>
+        <v>2.32976738056594</v>
       </c>
       <c r="C14">
         <v>216.89590882303355</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.3736565563708467</v>
+        <v>-3.456143223397707</v>
       </c>
       <c r="B15">
-        <v>2.2811059281907391</v>
+        <v>2.0370602384337193</v>
       </c>
       <c r="C15">
         <v>216.89590882303355</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.4505053532443557</v>
+        <v>-2.5339535052650017</v>
       </c>
       <c r="B16">
-        <v>1.9916730134256506</v>
+        <v>1.7447168514094529</v>
       </c>
       <c r="C16">
         <v>216.89590882303355</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.5283156804307694</v>
+        <v>-1.6127915186182544</v>
       </c>
       <c r="B17">
-        <v>1.6994385282252433</v>
+        <v>1.44939358197171</v>
       </c>
       <c r="C17">
         <v>216.89590882303355</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.609135429475216</v>
+        <v>-0.69414635156842019</v>
       </c>
       <c r="B18">
-        <v>1.3984356171190655</v>
+        <v>1.1467728554090326</v>
       </c>
       <c r="C18">
         <v>216.89590882303355</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.30692610365713519</v>
+        <v>0.22190255690183261</v>
       </c>
       <c r="B19">
-        <v>1.0883458290498878</v>
+        <v>0.8366243403259</v>
       </c>
       <c r="C19">
         <v>216.89590882303355</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.2202442718961168</v>
+        <v>1.1356281800919192</v>
       </c>
       <c r="B20">
-        <v>0.77026281406378194</v>
+        <v>0.51973951615577019</v>
       </c>
       <c r="C20">
         <v>216.89590882303355</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.1311944281715487</v>
+        <v>2.0473034913012427</v>
       </c>
       <c r="B21">
-        <v>0.44528022220682473</v>
+        <v>0.19690986233210708</v>
       </c>
       <c r="C21">
         <v>216.89590882303355</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.0400851177448742</v>
+        <v>2.9571528739263151</v>
       </c>
       <c r="B22">
-        <v>0.11429704883131245</v>
+        <v>-0.13121402695170686</v>
       </c>
       <c r="C22">
         <v>216.89590882303355</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>3.9469576552039625</v>
+        <v>3.8652063517520245</v>
       </c>
       <c r="B23">
-        <v>-0.22256632948555211</v>
+        <v>-0.4645450984625889</v>
       </c>
       <c r="C23">
         <v>216.89590882303355</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4.8517865474683051</v>
+        <v>4.771445358660368</v>
       </c>
       <c r="B24">
-        <v>-0.565384190860347</v>
+        <v>-0.80313718420753666</v>
       </c>
       <c r="C24">
         <v>216.89590882303355</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5.7545463014573874</v>
+        <v>5.6758513285333336</v>
       </c>
       <c r="B25">
-        <v>-0.91423081340964474</v>
+        <v>-1.1470441161935443</v>
       </c>
       <c r="C25">
         <v>216.89590882303355</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>6.65520042198534</v>
+        <v>6.5783976856013222</v>
       </c>
       <c r="B26">
-        <v>-1.269212531621688</v>
+        <v>-1.4963429502173109</v>
       </c>
       <c r="C26">
         <v>216.89590882303355</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>7.553668405444891</v>
+        <v>7.4790258154883889</v>
       </c>
       <c r="B27">
-        <v>-1.630563905471397</v>
+        <v>-1.8512036372343579</v>
       </c>
       <c r="C27">
         <v>216.89590882303355</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>8.4498587461234127</v>
+        <v>8.3776690941670076</v>
       </c>
       <c r="B28">
-        <v>-1.9985515513053616</v>
+        <v>-2.2118193519899108</v>
       </c>
       <c r="C28">
         <v>216.89590882303355</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>9.3436799383082789</v>
+        <v>9.2742608976096417</v>
       </c>
       <c r="B29">
-        <v>-2.3734420854701681</v>
+        <v>-2.5783832692291933</v>
       </c>
       <c r="C29">
         <v>216.89590882303355</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>10.23509026211352</v>
+        <v>10.168770794961144</v>
       </c>
       <c r="B30">
-        <v>-2.755357065442996</v>
+        <v>-2.9509836224755519</v>
       </c>
       <c r="C30">
         <v>216.89590882303355</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>11.124247140959861</v>
+        <v>11.061313128055948</v>
       </c>
       <c r="B31">
-        <v>-3.1438378132233993</v>
+        <v>-3.3292888803648291</v>
       </c>
       <c r="C31">
         <v>216.89590882303355</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>12.011357784094676</v>
+        <v>11.952038431900869</v>
       </c>
       <c r="B32">
-        <v>-3.5382805919415254</v>
+        <v>-3.7128625703109908</v>
       </c>
       <c r="C32">
         <v>216.89590882303355</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>12.89662940076534</v>
+        <v>12.841097241502723</v>
       </c>
       <c r="B33">
-        <v>-3.9380816647275156</v>
+        <v>-4.1012682197279995</v>
       </c>
       <c r="C33">
         <v>216.89590882303355</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>13.780188774806954</v>
+        <v>13.728581599543434</v>
       </c>
       <c r="B34">
-        <v>-4.342871626853</v>
+        <v>-4.494238953101295</v>
       </c>
       <c r="C34">
         <v>216.89590882303355</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>14.661840988405437</v>
+        <v>14.61434957940534</v>
       </c>
       <c r="B35">
-        <v>-4.7532184021555235</v>
+        <v>-4.8921862832022036</v>
       </c>
       <c r="C35">
         <v>216.89590882303355</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>15.541310698334423</v>
+        <v>15.49820076214588</v>
       </c>
       <c r="B36">
-        <v>-5.1699242466141069</v>
+        <v>-5.2956913198735247</v>
       </c>
       <c r="C36">
         <v>216.89590882303355</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>16.418322561367564</v>
+        <v>16.379934728822512</v>
       </c>
       <c r="B37">
-        <v>-5.5937914162077815</v>
+        <v>-5.7053351729580646</v>
       </c>
       <c r="C37">
         <v>216.89590882303355</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>17.292403984543412</v>
+        <v>17.259207618528865</v>
       </c>
       <c r="B38">
-        <v>-6.0261968851732384</v>
+        <v>-6.12211485877919</v>
       </c>
       <c r="C38">
         <v>216.89590882303355</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>18.162293375960314</v>
+        <v>18.135101802503371</v>
       </c>
       <c r="B39">
-        <v>-6.4708165007778273</v>
+        <v>-6.5486910195825532</v>
       </c>
       <c r="C39">
         <v>216.89590882303355</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>19.02653189398152</v>
+        <v>19.00655621002063</v>
       </c>
       <c r="B40">
-        <v>-6.931900828546568</v>
+        <v>-6.9881402040943748</v>
       </c>
       <c r="C40">
         <v>216.89590882303355</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>19.883660696970285</v>
+        <v>19.872509770355261</v>
       </c>
       <c r="B41">
-        <v>-7.4137004340044745</v>
+        <v>-7.44353896104087</v>
       </c>
       <c r="C41">
         <v>216.89590882303355</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>19.883660696970285</v>
+        <v>19.872509770355261</v>
       </c>
       <c r="B42">
-        <v>-7.4137004340044745</v>
+        <v>-7.44353896104087</v>
       </c>
       <c r="C42">
         <v>216.89590882303355</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>18.957637910309554</v>
+        <v>18.95645886912358</v>
       </c>
       <c r="B43">
-        <v>-7.1326343314179548</v>
+        <v>-7.1333962239209807</v>
       </c>
       <c r="C43">
         <v>216.89590882303355</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>18.036337405445142</v>
+        <v>18.043510942799827</v>
       </c>
       <c r="B44">
-        <v>-6.8378091149582039</v>
+        <v>-6.8142564866274746</v>
       </c>
       <c r="C44">
         <v>216.89590882303355</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>17.118302152715025</v>
+        <v>17.13260674055617</v>
       </c>
       <c r="B45">
-        <v>-6.5334700706757589</v>
+        <v>-6.4891910211379509</v>
       </c>
       <c r="C45">
         <v>216.89590882303355</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>16.202075122457163</v>
+        <v>16.222687011564787</v>
       </c>
       <c r="B46">
-        <v>-6.2238624846211517</v>
+        <v>-6.161271099430004</v>
       </c>
       <c r="C46">
         <v>216.89590882303355</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>15.286396471795927</v>
+        <v>15.312835883737737</v>
       </c>
       <c r="B47">
-        <v>-5.9126571079980978</v>
+        <v>-5.8331522703168082</v>
       </c>
       <c r="C47">
         <v>216.89590882303355</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>14.370795105001328</v>
+        <v>14.40271099994675</v>
       </c>
       <c r="B48">
-        <v>-5.60122655262303</v>
+        <v>-5.50582718995385</v>
       </c>
       <c r="C48">
         <v>216.89590882303355</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>13.454997113129769</v>
+        <v>13.492113381803421</v>
       </c>
       <c r="B49">
-        <v>-5.290368895465555</v>
+        <v>-5.1798727913321869</v>
       </c>
       <c r="C49">
         <v>216.89590882303355</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>12.53872858723768</v>
+        <v>12.580844050919378</v>
       </c>
       <c r="B50">
-        <v>-4.9808822134952893</v>
+        <v>-4.8558660074428825</v>
       </c>
       <c r="C50">
         <v>216.89590882303355</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>11.621795973631008</v>
+        <v>11.668762450761593</v>
       </c>
       <c r="B51">
-        <v>-4.6733304559706292</v>
+        <v>-4.534214378530244</v>
       </c>
       <c r="C51">
         <v>216.89590882303355</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>10.70432713961385</v>
+        <v>10.755961712218454</v>
       </c>
       <c r="B52">
-        <v>-4.3673410613051171</v>
+        <v>-4.2146478738515523</v>
       </c>
       <c r="C52">
         <v>216.89590882303355</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>9.78653030773984</v>
+        <v>9.8425933880337126</v>
       </c>
       <c r="B53">
-        <v>-4.0623073402010865</v>
+        <v>-3.8967270699173313</v>
       </c>
       <c r="C53">
         <v>216.89590882303355</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>8.8686137005626158</v>
+        <v>8.9288090309511166</v>
       </c>
       <c r="B54">
-        <v>-3.7576226033608644</v>
+        <v>-3.580012543238106</v>
       </c>
       <c r="C54">
         <v>216.89590882303355</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>7.9507356871887875</v>
+        <v>8.0147239326259978</v>
       </c>
       <c r="B55">
-        <v>-3.4528254173787349</v>
+        <v>-3.2641700084670986</v>
       </c>
       <c r="C55">
         <v>216.89590882303355</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>7.0328552229369459</v>
+        <v>7.1003083403600922</v>
       </c>
       <c r="B56">
-        <v>-3.1480353724168064</v>
+        <v>-2.9492857328283333</v>
       </c>
       <c r="C56">
         <v>216.89590882303355</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>6.1148814096786612</v>
+        <v>6.1854962403667262</v>
       </c>
       <c r="B57">
-        <v>-2.8435173145291421</v>
+        <v>-2.6355511216885348</v>
       </c>
       <c r="C57">
         <v>216.89590882303355</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5.1967233492855041</v>
+        <v>5.2702216188592192</v>
       </c>
       <c r="B58">
-        <v>-2.5395360897698014</v>
+        <v>-2.3231575804144242</v>
       </c>
       <c r="C58">
         <v>216.89590882303355</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.27830107865017</v>
+        <v>4.3544264043249354</v>
       </c>
       <c r="B59">
-        <v>-2.236324683281651</v>
+        <v>-2.0122734859425746</v>
       </c>
       <c r="C59">
         <v>216.89590882303355</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.3595783747498884</v>
+        <v>3.4380842943474015</v>
       </c>
       <c r="B60">
-        <v>-1.9339886365627841</v>
+        <v>-1.7029751014889651</v>
       </c>
       <c r="C60">
         <v>216.89590882303355</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.4405299495830182</v>
+        <v>2.5211769287841892</v>
       </c>
       <c r="B61">
-        <v>-1.6326016302000979</v>
+        <v>-1.3953156618394271</v>
       </c>
       <c r="C61">
         <v>216.89590882303355</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.521130515147908</v>
+        <v>1.603685947492858</v>
       </c>
       <c r="B62">
-        <v>-1.3322373447804876</v>
+        <v>-1.0893484017797879</v>
       </c>
       <c r="C62">
         <v>216.89590882303355</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.601421521424068</v>
+        <v>0.68564151024193387</v>
       </c>
       <c r="B63">
-        <v>-1.0327750092418679</v>
+        <v>-0.78498587379575924</v>
       </c>
       <c r="C63">
         <v>216.89590882303355</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.31828862968441979</v>
+        <v>-0.23273214355626012</v>
       </c>
       <c r="B64">
-        <v>-0.73331604592621225</v>
+        <v>-0.48157790117256793</v>
       </c>
       <c r="C64">
         <v>216.89590882303355</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.2376247982923139</v>
+        <v>-1.1511622545784359</v>
       </c>
       <c r="B65">
-        <v>-0.43276742552651393</v>
+        <v>-0.17833362489532509</v>
       </c>
       <c r="C65">
         <v>216.89590882303355</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.156211844514385</v>
+        <v>-2.0693760635013181</v>
       </c>
       <c r="B66">
-        <v>-0.13003611873576182</v>
+        <v>0.12553781405086306</v>
       </c>
       <c r="C66">
         <v>216.89590882303355</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.0741593333771542</v>
+        <v>-2.9874532795453965</v>
       </c>
       <c r="B67">
-        <v>0.17455863943603875</v>
+        <v>0.42980530072246376</v>
       </c>
       <c r="C67">
         <v>216.89590882303355</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-3.9935156495541921</v>
+        <v>-3.9068834861062678</v>
       </c>
       <c r="B68">
-        <v>0.47504855671083429</v>
+        <v>0.7301498243422585</v>
       </c>
       <c r="C68">
         <v>216.89590882303355</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-4.9158673418938568</v>
+        <v>-4.8288204466182778</v>
       </c>
       <c r="B69">
-        <v>0.7668109724318819</v>
+        <v>1.023226075931911</v>
       </c>
       <c r="C69">
         <v>216.89590882303355</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-5.8390147962965928</v>
+        <v>-5.7516647704956281</v>
       </c>
       <c r="B70">
-        <v>1.0562548096957223</v>
+        <v>1.313671449542289</v>
       </c>
       <c r="C70">
         <v>216.89590882303355</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-6.7605598169332444</v>
+        <v>-6.6736726738118142</v>
       </c>
       <c r="B71">
-        <v>1.350367590833063</v>
+        <v>1.6065420041990286</v>
       </c>
       <c r="C71">
         <v>216.89590882303355</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-7.6810960440041063</v>
+        <v>-7.5952759532975724</v>
       </c>
       <c r="B72">
-        <v>1.647419651357974</v>
+        <v>1.9005857557976009</v>
       </c>
       <c r="C72">
         <v>216.89590882303355</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-8.6016152029555286</v>
+        <v>-8.5171958893005737</v>
       </c>
       <c r="B73">
-        <v>1.94452144254469</v>
+        <v>2.1937113695364903</v>
       </c>
       <c r="C73">
         <v>216.89590882303355</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-9.5217095241885943</v>
+        <v>-9.4391361159789238</v>
       </c>
       <c r="B74">
-        <v>2.2428610655247279</v>
+        <v>2.4867781509563827</v>
       </c>
       <c r="C74">
         <v>216.89590882303355</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-10.440613711688533</v>
+        <v>-10.360540295923524</v>
       </c>
       <c r="B75">
-        <v>2.5446683311116058</v>
+        <v>2.7813991868255319</v>
       </c>
       <c r="C75">
         <v>216.89590882303355</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-11.357531858822441</v>
+        <v>-11.280829851646061</v>
       </c>
       <c r="B76">
-        <v>2.8522622389895753</v>
+        <v>3.0792520484802668</v>
       </c>
       <c r="C76">
         <v>216.89590882303355</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-12.271727045360471</v>
+        <v>-12.199469108202077</v>
       </c>
       <c r="B77">
-        <v>3.1677899226409547</v>
+        <v>3.3818899123758155</v>
       </c>
       <c r="C77">
         <v>216.89590882303355</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-13.182728907303194</v>
+        <v>-13.116116240901873</v>
       </c>
       <c r="B78">
-        <v>3.4926218618696283</v>
+        <v>3.6903038908749464</v>
       </c>
       <c r="C78">
         <v>216.89590882303355</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-14.089735845499462</v>
+        <v>-14.030188571134127</v>
       </c>
       <c r="B79">
-        <v>3.8290936424108359</v>
+        <v>4.006183446420243</v>
       </c>
       <c r="C79">
         <v>216.89590882303355</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-14.991341776436688</v>
+        <v>-14.940663877695856</v>
       </c>
       <c r="B80">
-        <v>4.1813021106620107</v>
+        <v>4.3324924844938844</v>
       </c>
       <c r="C80">
         <v>216.89590882303355</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-15.884094166287786</v>
+        <v>-15.845031844579291</v>
       </c>
       <c r="B81">
-        <v>4.55930676923796</v>
+        <v>4.6765096052224724</v>
       </c>
       <c r="C81">
         <v>216.89590882303355</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-16.705832242249819</v>
+        <v>-16.698091553425037</v>
       </c>
       <c r="B82">
-        <v>5.1442228476678373</v>
+        <v>5.1692937705354778</v>
       </c>
       <c r="C82">
         <v>216.89590882303355</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-19.00842956797316</v>
+        <v>-18.995454665288271</v>
       </c>
       <c r="B1">
-        <v>4.8838621606886621</v>
+        <v>4.9340861670810829</v>
       </c>
       <c r="C1">
         <v>237.49899054506031</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-17.883410326866503</v>
+        <v>-17.892284276779471</v>
       </c>
       <c r="B2">
-        <v>4.8742615765555231</v>
+        <v>4.8441548438300073</v>
       </c>
       <c r="C2">
         <v>237.49899054506031</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-16.799421198786657</v>
+        <v>-16.81696875875145</v>
       </c>
       <c r="B3">
-        <v>4.7177107177752653</v>
+        <v>4.6554691393131238</v>
       </c>
       <c r="C3">
         <v>237.49899054506031</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-15.721761088709728</v>
+        <v>-15.746155052990536</v>
       </c>
       <c r="B4">
-        <v>4.5384923383579663</v>
+        <v>4.4508230775107753</v>
       </c>
       <c r="C4">
         <v>237.49899054506031</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-14.648501942032473</v>
+        <v>-14.67854554933907</v>
       </c>
       <c r="B5">
-        <v>4.3435118093245872</v>
+        <v>4.2348170994242365</v>
       </c>
       <c r="C5">
         <v>237.49899054506031</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-13.578858144431841</v>
+        <v>-13.613611475817912</v>
       </c>
       <c r="B6">
-        <v>4.1355828260812935</v>
+        <v>4.0093258700125851</v>
       </c>
       <c r="C6">
         <v>237.49899054506031</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-12.512381577800792</v>
+        <v>-12.55105119248905</v>
       </c>
       <c r="B7">
-        <v>3.916310333729295</v>
+        <v>3.7754187988594778</v>
       </c>
       <c r="C7">
         <v>237.49899054506031</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-11.448809057248507</v>
+        <v>-11.490687517637936</v>
       </c>
       <c r="B8">
-        <v>3.6866369348873818</v>
+        <v>3.5337240515348785</v>
       </c>
       <c r="C8">
         <v>237.49899054506031</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-10.387728654663189</v>
+        <v>-10.432243175148276</v>
       </c>
       <c r="B9">
-        <v>3.4480379593730444</v>
+        <v>3.2852246601201136</v>
       </c>
       <c r="C9">
         <v>237.49899054506031</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-9.3286955419913209</v>
+        <v>-9.37541875105108</v>
       </c>
       <c r="B10">
-        <v>3.20210656888664</v>
+        <v>3.0309821424302177</v>
       </c>
       <c r="C10">
         <v>237.49899054506031</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-8.2712820346334688</v>
+        <v>-8.3199263743682454</v>
       </c>
       <c r="B11">
-        <v>2.9503745254612852</v>
+        <v>2.7720170927036891</v>
       </c>
       <c r="C11">
         <v>237.49899054506031</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-7.215260059311472</v>
+        <v>-7.26561251050535</v>
       </c>
       <c r="B12">
-        <v>2.6936586786835961</v>
+        <v>2.5088738399434147</v>
       </c>
       <c r="C12">
         <v>237.49899054506031</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-6.1611828445781889</v>
+        <v>-6.212849427411836</v>
       </c>
       <c r="B13">
-        <v>2.4299776280214438</v>
+        <v>2.2402325757863584</v>
       </c>
       <c r="C13">
         <v>237.49899054506031</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-5.1093814223166927</v>
+        <v>-5.1618598632061561</v>
       </c>
       <c r="B14">
-        <v>2.1581457753239688</v>
+        <v>1.9653036227114282</v>
       </c>
       <c r="C14">
         <v>237.49899054506031</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-4.0585167358998984</v>
+        <v>-4.1117426341389383</v>
       </c>
       <c r="B15">
-        <v>1.8829589820841395</v>
+        <v>1.6872819639312229</v>
       </c>
       <c r="C15">
         <v>237.49899054506031</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.0073606089262</v>
+        <v>-3.0616711787497293</v>
       </c>
       <c r="B16">
-        <v>1.6088159897681005</v>
+        <v>1.409098022894028</v>
       </c>
       <c r="C16">
         <v>237.49899054506031</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.9567984744060196</v>
+        <v>-2.0122413466014977</v>
       </c>
       <c r="B17">
-        <v>1.3325456000908511</v>
+        <v>1.1286393232571592</v>
       </c>
       <c r="C17">
         <v>237.49899054506031</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.90797361127814846</v>
+        <v>-0.96422251467743159</v>
       </c>
       <c r="B18">
-        <v>1.0500531337629926</v>
+        <v>0.84317817874447643</v>
       </c>
       <c r="C18">
         <v>237.49899054506031</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.13905292721724064</v>
+        <v>0.0823442413819052</v>
       </c>
       <c r="B19">
-        <v>0.76111992722866206</v>
+        <v>0.55256896313696147</v>
       </c>
       <c r="C19">
         <v>237.49899054506031</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.1844906442646246</v>
+        <v>1.1275999212715981</v>
       </c>
       <c r="B20">
-        <v>0.46649632086538145</v>
+        <v>0.25731156522987847</v>
       </c>
       <c r="C20">
         <v>237.49899054506031</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.22854904304848</v>
+        <v>2.1716855246867333</v>
       </c>
       <c r="B21">
-        <v>0.16693265505067217</v>
+        <v>-0.04209412618150872</v>
       </c>
       <c r="C21">
         <v>237.49899054506031</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.2714003428317282</v>
+        <v>3.2147169571429557</v>
       </c>
       <c r="B22">
-        <v>-0.13695426304339653</v>
+        <v>-0.34523718915481549</v>
       </c>
       <c r="C22">
         <v>237.49899054506031</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.3130676271910691</v>
+        <v>4.2567097474381512</v>
       </c>
       <c r="B23">
-        <v>-0.44508175906656738</v>
+        <v>-0.65206256915917593</v>
       </c>
       <c r="C23">
         <v>237.49899054506031</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.3535366957816386</v>
+        <v>5.2976543301907544</v>
       </c>
       <c r="B24">
-        <v>-0.75750069187403279</v>
+        <v>-0.96260417851660052</v>
       </c>
       <c r="C24">
         <v>237.49899054506031</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>6.3927933482585839</v>
+        <v>6.3375411400192148</v>
       </c>
       <c r="B25">
-        <v>-1.0742619203209891</v>
+        <v>-1.2768959295491038</v>
       </c>
       <c r="C25">
         <v>237.49899054506031</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>7.4308172525953351</v>
+        <v>7.37635648216327</v>
       </c>
       <c r="B26">
-        <v>-1.3954382640188516</v>
+        <v>-1.5949863745404265</v>
       </c>
       <c r="C26">
         <v>237.49899054506031</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>8.4675635500385411</v>
+        <v>8.4140701443479049</v>
       </c>
       <c r="B27">
-        <v>-1.7211903856039326</v>
+        <v>-1.9169826256212403</v>
       </c>
       <c r="C27">
         <v>237.49899054506031</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>9.50298125015314</v>
+        <v>9.4506477849194024</v>
       </c>
       <c r="B28">
-        <v>-2.0517009084687654</v>
+        <v>-2.2430064348839447</v>
       </c>
       <c r="C28">
         <v>237.49899054506031</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>10.537019362504053</v>
+        <v>10.486055062224038</v>
       </c>
       <c r="B29">
-        <v>-2.387152456005881</v>
+        <v>-2.5731795544209386</v>
       </c>
       <c r="C29">
         <v>237.49899054506031</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>11.569654699035075</v>
+        <v>11.520276341995739</v>
       </c>
       <c r="B30">
-        <v>-2.7276280767613108</v>
+        <v>-2.9075574126814043</v>
       </c>
       <c r="C30">
         <v>237.49899054506031</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>12.600975281205336</v>
+        <v>12.553370819518987</v>
       </c>
       <c r="B31">
-        <v>-3.0728125198950615</v>
+        <v>-3.2459301435416448</v>
       </c>
       <c r="C31">
         <v>237.49899054506031</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>13.631096932852842</v>
+        <v>13.585416397465931</v>
       </c>
       <c r="B32">
-        <v>-3.4222909597206472</v>
+        <v>-3.5880215572347542</v>
       </c>
       <c r="C32">
         <v>237.49899054506031</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>14.660135477815583</v>
+        <v>14.616490978508704</v>
       </c>
       <c r="B33">
-        <v>-3.7756485705515743</v>
+        <v>-3.93355546399382</v>
       </c>
       <c r="C33">
         <v>237.49899054506031</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>15.688161854260367</v>
+        <v>15.646642255357678</v>
       </c>
       <c r="B34">
-        <v>-4.1326312857443757</v>
+        <v>-4.2823627779812927</v>
       </c>
       <c r="C34">
         <v>237.49899054506031</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>16.715067457669363</v>
+        <v>16.675797080876251</v>
       </c>
       <c r="B35">
-        <v>-4.4936280748276989</v>
+        <v>-4.6347028290771011</v>
       </c>
       <c r="C35">
         <v>237.49899054506031</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>17.740698797853568</v>
+        <v>17.703852097966063</v>
       </c>
       <c r="B36">
-        <v>-4.8591886663732229</v>
+        <v>-4.9909420510905393</v>
       </c>
       <c r="C36">
         <v>237.49899054506031</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>18.764902384623973</v>
+        <v>18.73070394952876</v>
       </c>
       <c r="B37">
-        <v>-5.2298627889526195</v>
+        <v>-5.3514468778309006</v>
       </c>
       <c r="C37">
         <v>237.49899054506031</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>19.787414625644676</v>
+        <v>19.756175179760149</v>
       </c>
       <c r="B38">
-        <v>-5.6065945044584469</v>
+        <v>-5.716846446603161</v>
       </c>
       <c r="C38">
         <v>237.49899054506031</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>20.807531519992189</v>
+        <v>20.779791938032719</v>
       </c>
       <c r="B39">
-        <v>-5.9919052080667656</v>
+        <v>-6.0888207086950228</v>
       </c>
       <c r="C39">
         <v>237.49899054506031</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>21.824438964596112</v>
+        <v>21.801006275013119</v>
       </c>
       <c r="B40">
-        <v>-6.3887106282745183</v>
+        <v>-6.4693123188898687</v>
       </c>
       <c r="C40">
         <v>237.49899054506031</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>22.837322856386059</v>
+        <v>22.819270241367992</v>
       </c>
       <c r="B41">
-        <v>-6.7999264935786474</v>
+        <v>-6.860263931971085</v>
       </c>
       <c r="C41">
         <v>237.49899054506031</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>22.837322856386059</v>
+        <v>22.819270241367992</v>
       </c>
       <c r="B42">
-        <v>-6.7999264935786474</v>
+        <v>-6.860263931971085</v>
       </c>
       <c r="C42">
         <v>237.49899054506031</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>21.785979926741568</v>
+        <v>21.77512429612473</v>
       </c>
       <c r="B43">
-        <v>-6.526452539238691</v>
+        <v>-6.5610721715454874</v>
       </c>
       <c r="C43">
         <v>237.49899054506031</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>20.737218479870808</v>
+        <v>20.732473005435324</v>
       </c>
       <c r="B44">
-        <v>-6.24373294615656</v>
+        <v>-6.2565813850205272</v>
       </c>
       <c r="C44">
         <v>237.49899054506031</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>19.690224877223176</v>
+        <v>19.690768888881877</v>
       </c>
       <c r="B45">
-        <v>-5.9546817791410831</v>
+        <v>-5.948732564725062</v>
       </c>
       <c r="C45">
         <v>237.49899054506031</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>18.64418548024808</v>
+        <v>18.649464466046489</v>
       </c>
       <c r="B46">
-        <v>-5.6622131030010987</v>
+        <v>-5.63946670298795</v>
       </c>
       <c r="C46">
         <v>237.49899054506031</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>17.598396736547524</v>
+        <v>17.608086339071448</v>
       </c>
       <c r="B47">
-        <v>-5.368846706508493</v>
+        <v>-5.3304621458838213</v>
       </c>
       <c r="C47">
         <v>237.49899054506031</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>16.552595438333917</v>
+        <v>16.566457440339796</v>
       </c>
       <c r="B48">
-        <v>-5.0755252742873607</v>
+        <v>-5.022346654470403</v>
       </c>
       <c r="C48">
         <v>237.49899054506031</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>15.506628463972275</v>
+        <v>15.524474784794743</v>
       </c>
       <c r="B49">
-        <v>-4.7827972149248525</v>
+        <v>-4.7154853435511956</v>
       </c>
       <c r="C49">
         <v>237.49899054506031</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>14.460342691827611</v>
+        <v>14.48203538737951</v>
       </c>
       <c r="B50">
-        <v>-4.491210937008117</v>
+        <v>-4.4102433279297006</v>
       </c>
       <c r="C50">
         <v>237.49899054506031</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>13.413629867997909</v>
+        <v>13.439066454891121</v>
       </c>
       <c r="B51">
-        <v>-4.2011541543273045</v>
+        <v>-4.1068786826784409</v>
       </c>
       <c r="C51">
         <v>237.49899054506031</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>12.366561209513074</v>
+        <v>12.395615961541873</v>
       </c>
       <c r="B52">
-        <v>-3.9123718014845745</v>
+        <v>-3.8052213239460482</v>
       </c>
       <c r="C52">
         <v>237.49899054506031</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>11.319252801135987</v>
+        <v>11.351762073397866</v>
       </c>
       <c r="B53">
-        <v>-3.6244481182850841</v>
+        <v>-3.5049941281501726</v>
       </c>
       <c r="C53">
         <v>237.49899054506031</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>10.271820727629494</v>
+        <v>10.307582956525179</v>
       </c>
       <c r="B54">
-        <v>-3.3369673445339862</v>
+        <v>-3.205919971708461</v>
       </c>
       <c r="C54">
         <v>237.49899054506031</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>9.2243532539983324</v>
+        <v>9.2631380520585118</v>
       </c>
       <c r="B55">
-        <v>-3.0496133571273538</v>
+        <v>-2.9077881168800408</v>
       </c>
       <c r="C55">
         <v>237.49899054506031</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>8.1768273662145781</v>
+        <v>8.2184119014068866</v>
       </c>
       <c r="B56">
-        <v>-2.7624685813248973</v>
+        <v>-2.6106533692899268</v>
       </c>
       <c r="C56">
         <v>237.49899054506031</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>7.1291922304921744</v>
+        <v>7.17337032104793</v>
       </c>
       <c r="B57">
-        <v>-2.4757150794772413</v>
+        <v>-2.3146369204046078</v>
       </c>
       <c r="C57">
         <v>237.49899054506031</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>6.0813970130450521</v>
+        <v>6.1279791274592563</v>
       </c>
       <c r="B58">
-        <v>-2.1895349139350109</v>
+        <v>-2.0198599616905719</v>
       </c>
       <c r="C58">
         <v>237.49899054506031</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5.0333969944787862</v>
+        <v>5.0822082490435081</v>
       </c>
       <c r="B59">
-        <v>-1.9040882482172907</v>
+        <v>-1.7264291065313457</v>
       </c>
       <c r="C59">
         <v>237.49899054506031</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.9851719129656</v>
+        <v>4.0360440619034925</v>
       </c>
       <c r="B60">
-        <v>-1.6194476505170321</v>
+        <v>-1.4343926559786273</v>
       </c>
       <c r="C60">
         <v>237.49899054506031</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.9367076210693459</v>
+        <v>2.9894770540670281</v>
       </c>
       <c r="B61">
-        <v>-1.3356637901956467</v>
+        <v>-1.1437843330011501</v>
       </c>
       <c r="C61">
         <v>237.49899054506031</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.8879899713538968</v>
+        <v>1.9424977135619517</v>
       </c>
       <c r="B62">
-        <v>-1.05278733661455</v>
+        <v>-0.85463786056765279</v>
       </c>
       <c r="C62">
         <v>237.49899054506031</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.83904208232668365</v>
+        <v>0.89512160444742339</v>
       </c>
       <c r="B63">
-        <v>-0.77073549031825761</v>
+        <v>-0.5668980591348044</v>
       </c>
       <c r="C63">
         <v>237.49899054506031</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.20996386373057183</v>
+        <v>-0.15253540509205743</v>
       </c>
       <c r="B64">
-        <v>-0.48889157658370036</v>
+        <v>-0.28015413911101256</v>
       </c>
       <c r="C64">
         <v>237.49899054506031</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.2588184185925768</v>
+        <v>-1.200332370840657</v>
       </c>
       <c r="B65">
-        <v>-0.20650545187091168</v>
+        <v>0.00609359160738096</v>
       </c>
       <c r="C65">
         <v>237.49899054506031</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.307312134034039</v>
+        <v>-2.248128348582541</v>
       </c>
       <c r="B66">
-        <v>0.07717302736007442</v>
+        <v>0.29234482512403415</v>
       </c>
       <c r="C66">
         <v>237.49899054506031</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.3555061326959819</v>
+        <v>-3.2959644840158537</v>
       </c>
       <c r="B67">
-        <v>0.36192494899270161</v>
+        <v>0.57845368684353737</v>
       </c>
       <c r="C67">
         <v>237.49899054506031</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.4045438206846788</v>
+        <v>-4.3446102824946244</v>
       </c>
       <c r="B68">
-        <v>0.643655178284317</v>
+        <v>0.86169203537420191</v>
       </c>
       <c r="C68">
         <v>237.49899054506031</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.4553107790030939</v>
+        <v>-5.39466174297479</v>
       </c>
       <c r="B69">
-        <v>0.919191986911338</v>
+        <v>1.1399468647277722</v>
       </c>
       <c r="C69">
         <v>237.49899054506031</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-6.506579004775638</v>
+        <v>-6.4452924791639568</v>
       </c>
       <c r="B70">
-        <v>1.1929334948525368</v>
+        <v>1.4161479773259771</v>
       </c>
       <c r="C70">
         <v>237.49899054506031</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-7.5570096306309757</v>
+        <v>-7.4956014983593917</v>
       </c>
       <c r="B71">
-        <v>1.4696748857772</v>
+        <v>1.6934896790603218</v>
       </c>
       <c r="C71">
         <v>237.49899054506031</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-8.6069339150932613</v>
+        <v>-8.5458117674652918</v>
       </c>
       <c r="B72">
-        <v>1.7482297498142936</v>
+        <v>1.9711814812914084</v>
       </c>
       <c r="C72">
         <v>237.49899054506031</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-9.65690533129726</v>
+        <v>-9.5962958013274378</v>
       </c>
       <c r="B73">
-        <v>2.0266158104560441</v>
+        <v>2.2479027003300711</v>
       </c>
       <c r="C73">
         <v>237.49899054506031</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-10.706696084924687</v>
+        <v>-10.646900346951027</v>
       </c>
       <c r="B74">
-        <v>2.3056489181880373</v>
+        <v>2.5241966668189697</v>
       </c>
       <c r="C74">
         <v>237.49899054506031</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-11.755878787654943</v>
+        <v>-11.697337832440422</v>
       </c>
       <c r="B75">
-        <v>2.5868597739140515</v>
+        <v>2.8010829146540681</v>
       </c>
       <c r="C75">
         <v>237.49899054506031</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-12.804008942611304</v>
+        <v>-12.747309178137277</v>
       </c>
       <c r="B76">
-        <v>2.8718403532172889</v>
+        <v>3.0796217764127172</v>
       </c>
       <c r="C76">
         <v>237.49899054506031</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-13.850674970644372</v>
+        <v>-13.79653746018988</v>
       </c>
       <c r="B77">
-        <v>3.1620647360985226</v>
+        <v>3.3607950352862321</v>
       </c>
       <c r="C77">
         <v>237.49899054506031</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-14.895614072070226</v>
+        <v>-14.844845885735706</v>
       </c>
       <c r="B78">
-        <v>3.4584741455493897</v>
+        <v>3.6452294782403829</v>
       </c>
       <c r="C78">
         <v>237.49899054506031</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-15.938378530359845</v>
+        <v>-15.891933220214819</v>
       </c>
       <c r="B79">
-        <v>3.7626720884103468</v>
+        <v>3.9339930776645033</v>
       </c>
       <c r="C79">
         <v>237.49899054506031</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-16.978183165196945</v>
+        <v>-16.937271129761783</v>
       </c>
       <c r="B80">
-        <v>4.0774707056825692</v>
+        <v>4.22895894526523</v>
       </c>
       <c r="C80">
         <v>237.49899054506031</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-18.013100380928869</v>
+        <v>-17.979562467512459</v>
       </c>
       <c r="B81">
-        <v>4.4097737246451363</v>
+        <v>4.5347258795207512</v>
       </c>
       <c r="C81">
         <v>237.49899054506031</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-19.00842956797316</v>
+        <v>-18.995454665288271</v>
       </c>
       <c r="B82">
-        <v>4.8838621606886621</v>
+        <v>4.9340861670810829</v>
       </c>
       <c r="C82">
         <v>237.49899054506031</v>
